--- a/partial/sliding_window_results_window_1.xlsx
+++ b/partial/sliding_window_results_window_1.xlsx
@@ -463,13 +463,13 @@
         <v>28.98</v>
       </c>
       <c r="C2" t="n">
-        <v>28.61942153242016</v>
+        <v>29.89632680511049</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3605784675798382</v>
+        <v>0.9163268051104865</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1300168312822245</v>
+        <v>0.8396548137639914</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.15</v>
       </c>
       <c r="C3" t="n">
-        <v>28.28017903452562</v>
+        <v>29.74049686643244</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8698209654743749</v>
+        <v>0.5904968664324421</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7565885119787737</v>
+        <v>0.3486865492665334</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.35</v>
       </c>
       <c r="C4" t="n">
-        <v>28.88646415724472</v>
+        <v>30.17802841988026</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4635358427552845</v>
+        <v>0.8280284198802619</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2148654775188518</v>
+        <v>0.6856310641294032</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.37</v>
       </c>
       <c r="C5" t="n">
-        <v>28.79124348772752</v>
+        <v>29.89923241292755</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5787565122724807</v>
+        <v>0.529232412927545</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3349591004978061</v>
+        <v>0.2800869468931115</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.54</v>
       </c>
       <c r="C6" t="n">
-        <v>28.69696473790746</v>
+        <v>28.9817084540674</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8430352620925348</v>
+        <v>-0.5582915459325974</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7107084531314288</v>
+        <v>0.3116894502598095</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.55</v>
       </c>
       <c r="C7" t="n">
-        <v>29.86126388352603</v>
+        <v>29.32096095580385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3112638835260277</v>
+        <v>-0.2290390441961527</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09688520518770456</v>
+        <v>0.05245888376628721</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.75</v>
       </c>
       <c r="C8" t="n">
-        <v>29.59043104121293</v>
+        <v>29.6377051150338</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1595689587870659</v>
+        <v>-0.1122948849662038</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02546225260838833</v>
+        <v>0.01261014118957294</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>29.84</v>
       </c>
       <c r="C9" t="n">
-        <v>30.47360527894018</v>
+        <v>30.13562491976559</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6336052789401769</v>
+        <v>0.29562491976559</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4014556495008594</v>
+        <v>0.08739409318641153</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>29.81</v>
       </c>
       <c r="C10" t="n">
-        <v>30.35429894197885</v>
+        <v>30.02736367531402</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5442989419788482</v>
+        <v>0.2173636753140187</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2962613382392936</v>
+        <v>0.04724696734601813</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>29.92</v>
       </c>
       <c r="C11" t="n">
-        <v>30.19960459309228</v>
+        <v>29.79807864747706</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2796045930922801</v>
+        <v>-0.1219213525229428</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07817872847829956</v>
+        <v>0.01486481620102369</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>29.98</v>
       </c>
       <c r="C12" t="n">
-        <v>29.54863326317109</v>
+        <v>29.73481586349194</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4313667368289096</v>
+        <v>-0.2451841365080618</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1860772616424217</v>
+        <v>0.06011526079520389</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.04</v>
       </c>
       <c r="C13" t="n">
-        <v>29.85653219908905</v>
+        <v>29.74052743269053</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1834678009109503</v>
+        <v>-0.2994725673094685</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03366043397110009</v>
+        <v>0.08968381857092413</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.21</v>
       </c>
       <c r="C14" t="n">
-        <v>29.40461724422588</v>
+        <v>29.81772104667583</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8053827557741222</v>
+        <v>-0.3922789533241691</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6486413832983194</v>
+        <v>0.1538827772211056</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.22</v>
       </c>
       <c r="C15" t="n">
-        <v>29.82918319365324</v>
+        <v>29.83126696289785</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3908168063467627</v>
+        <v>-0.3887330371021527</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1527377761230831</v>
+        <v>0.1511133741346636</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.38</v>
       </c>
       <c r="C16" t="n">
-        <v>29.64636299647648</v>
+        <v>29.97346329811299</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7336370035235191</v>
+        <v>-0.4065367018870063</v>
       </c>
       <c r="E16" t="n">
-        <v>0.538223252938968</v>
+        <v>0.1652720899811646</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.44</v>
       </c>
       <c r="C17" t="n">
-        <v>30.33773402865503</v>
+        <v>30.04707284956853</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1022659713449734</v>
+        <v>-0.392927150431472</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01045832889513092</v>
+        <v>0.1543917455461966</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.48</v>
       </c>
       <c r="C18" t="n">
-        <v>30.36049336566984</v>
+        <v>29.91660694866449</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1195066343301612</v>
+        <v>-0.5633930513355061</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01428183564892286</v>
+        <v>0.3174117302931322</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>30.69</v>
       </c>
       <c r="C19" t="n">
-        <v>30.65505704903011</v>
+        <v>29.99936347057776</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.03494295096988864</v>
+        <v>-0.6906365294222425</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001221009822484041</v>
+        <v>0.4769788157724</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>30.75</v>
       </c>
       <c r="C20" t="n">
-        <v>30.32258370656307</v>
+        <v>30.42549840475123</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4274162934369308</v>
+        <v>-0.3245015952487691</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1826846878953645</v>
+        <v>0.105301285318996</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>30.94</v>
       </c>
       <c r="C21" t="n">
-        <v>30.73581033191036</v>
+        <v>30.47888267616282</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2041896680896436</v>
+        <v>-0.4611173238371791</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0416934205545588</v>
+        <v>0.2126291863427619</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>30.95</v>
       </c>
       <c r="C22" t="n">
-        <v>31.06682419096773</v>
+        <v>30.71352857353821</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1168241909677299</v>
+        <v>-0.2364714264617938</v>
       </c>
       <c r="E22" t="n">
-        <v>0.01364789159526462</v>
+        <v>0.05591873553287553</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.02</v>
       </c>
       <c r="C23" t="n">
-        <v>31.71203661379989</v>
+        <v>30.96141697364089</v>
       </c>
       <c r="D23" t="n">
-        <v>0.692036613799889</v>
+        <v>-0.05858302635910917</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4789146748396167</v>
+        <v>0.00343197097739208</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.12</v>
       </c>
       <c r="C24" t="n">
-        <v>32.12226057527928</v>
+        <v>31.1678367404652</v>
       </c>
       <c r="D24" t="n">
-        <v>1.002260575279283</v>
+        <v>0.04783674046520048</v>
       </c>
       <c r="E24" t="n">
-        <v>1.00452626075916</v>
+        <v>0.002288353738334949</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.28</v>
       </c>
       <c r="C25" t="n">
-        <v>32.26900250503424</v>
+        <v>31.10946212854389</v>
       </c>
       <c r="D25" t="n">
-        <v>0.989002505034243</v>
+        <v>-0.1705378714561085</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9781259549640079</v>
+        <v>0.0290831656007802</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>31.38</v>
       </c>
       <c r="C26" t="n">
-        <v>32.11758947928325</v>
+        <v>31.22930082036947</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7375894792832476</v>
+        <v>-0.1506991796305321</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5440382399493323</v>
+        <v>0.02271024274131539</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>31.58</v>
       </c>
       <c r="C27" t="n">
-        <v>32.53827326168924</v>
+        <v>31.5887951343716</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9582732616892429</v>
+        <v>0.008795134371599289</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9182876440685401</v>
+        <v>7.735438861448722e-05</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>31.65</v>
       </c>
       <c r="C28" t="n">
-        <v>32.52980955291806</v>
+        <v>31.96396303559739</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8798095529180614</v>
+        <v>0.3139630355973893</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7740648494058791</v>
+        <v>0.09857278772152751</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>31.88</v>
       </c>
       <c r="C29" t="n">
-        <v>33.277970159239</v>
+        <v>32.81493599015737</v>
       </c>
       <c r="D29" t="n">
-        <v>1.397970159238998</v>
+        <v>0.9349359901573742</v>
       </c>
       <c r="E29" t="n">
-        <v>1.954320566122709</v>
+        <v>0.8741053056915496</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>32.28</v>
       </c>
       <c r="C30" t="n">
-        <v>32.85379537904976</v>
+        <v>32.97279510279719</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5737953790497556</v>
+        <v>0.6927951027971844</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3292411370188528</v>
+        <v>0.4799650544597612</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>32.45</v>
       </c>
       <c r="C31" t="n">
-        <v>32.96916922584683</v>
+        <v>33.04564124508133</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5191692258468237</v>
+        <v>0.5956412450813247</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2695366850663902</v>
+        <v>0.3547884928420307</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>32.85</v>
       </c>
       <c r="C32" t="n">
-        <v>33.13367271978353</v>
+        <v>33.20541006560473</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2836727197835245</v>
+        <v>0.3554100656047297</v>
       </c>
       <c r="E32" t="n">
-        <v>0.080470211949382</v>
+        <v>0.1263163147331582</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>32.9</v>
       </c>
       <c r="C33" t="n">
-        <v>33.22534331497836</v>
+        <v>33.28618459035178</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3253433149783618</v>
+        <v>0.3861845903517818</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1058482726011095</v>
+        <v>0.1491385378251735</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>33.1</v>
       </c>
       <c r="C34" t="n">
-        <v>33.21840007594129</v>
+        <v>33.33682847309746</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1184000759412882</v>
+        <v>0.2368284730974537</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01401857798290281</v>
+        <v>0.05608772566967135</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>33.4</v>
       </c>
       <c r="C35" t="n">
-        <v>34.21330507641433</v>
+        <v>33.6759927999388</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8133050764143306</v>
+        <v>0.2759927999387983</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6614651473213201</v>
+        <v>0.07617202561805755</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>33.7</v>
       </c>
       <c r="C36" t="n">
-        <v>33.99777500965789</v>
+        <v>33.7170788925518</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2977750096578902</v>
+        <v>0.01707889255179396</v>
       </c>
       <c r="E36" t="n">
-        <v>0.08866995637675658</v>
+        <v>0.000291688570795723</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>34.1</v>
       </c>
       <c r="C37" t="n">
-        <v>34.04644958257992</v>
+        <v>33.82441943356593</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.05355041742008382</v>
+        <v>-0.2755805664340727</v>
       </c>
       <c r="E37" t="n">
-        <v>0.002867647205865216</v>
+        <v>0.07594464859612435</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>34.4</v>
       </c>
       <c r="C38" t="n">
-        <v>34.57601968097843</v>
+        <v>34.25753728015376</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1760196809784276</v>
+        <v>-0.142462719846236</v>
       </c>
       <c r="E38" t="n">
-        <v>0.03098292809174742</v>
+        <v>0.02029562654598714</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>34.9</v>
       </c>
       <c r="C39" t="n">
-        <v>34.85083618170182</v>
+        <v>34.55309186796224</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.04916381829818306</v>
+        <v>-0.3469081320377612</v>
       </c>
       <c r="E39" t="n">
-        <v>0.002417081029656759</v>
+        <v>0.1203452520739287</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>35.3</v>
       </c>
       <c r="C40" t="n">
-        <v>35.9687543924692</v>
+        <v>35.46894970214569</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6687543924692037</v>
+        <v>0.1689497021456958</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4472324374468536</v>
+        <v>0.02854400185511934</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>35.7</v>
       </c>
       <c r="C41" t="n">
-        <v>36.10000759518975</v>
+        <v>35.73876694052214</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4000075951897486</v>
+        <v>0.03876694052213736</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1600060762094858</v>
+        <v>0.001502875677446936</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>36.3</v>
       </c>
       <c r="C42" t="n">
-        <v>35.91907778380174</v>
+        <v>36.10449998253414</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3809222161982575</v>
+        <v>-0.1955000174658537</v>
       </c>
       <c r="E42" t="n">
-        <v>0.145101734793392</v>
+        <v>0.03822025682914908</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>36.8</v>
       </c>
       <c r="C43" t="n">
-        <v>36.40238053655096</v>
+        <v>36.68021591248571</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3976194634490327</v>
+        <v>-0.119784087514283</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1581012377134966</v>
+        <v>0.01434822762162942</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>37.3</v>
       </c>
       <c r="C44" t="n">
-        <v>36.34026366487587</v>
+        <v>36.80267619744119</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.959736335124127</v>
+        <v>-0.4973238025588103</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9210938329574907</v>
+        <v>0.2473309645915545</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>37.9</v>
       </c>
       <c r="C45" t="n">
-        <v>37.45542092048556</v>
+        <v>37.74713299675034</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4445790795144404</v>
+        <v>-0.1528670032496606</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1976505579419071</v>
+        <v>0.02336832068253175</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>38.5</v>
       </c>
       <c r="C46" t="n">
-        <v>38.17963449233827</v>
+        <v>38.41971972881053</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3203655076617338</v>
+        <v>-0.08028027118946568</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1026340584993604</v>
+        <v>0.006444921942254153</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>38.9</v>
       </c>
       <c r="C47" t="n">
-        <v>38.58431861107851</v>
+        <v>39.09180267373289</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3156813889214902</v>
+        <v>0.1918026737328873</v>
       </c>
       <c r="E47" t="n">
-        <v>0.09965473931140117</v>
+        <v>0.03678826565108441</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>39.4</v>
       </c>
       <c r="C48" t="n">
-        <v>38.90683823342697</v>
+        <v>39.59583476909648</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4931617665730244</v>
+        <v>0.1958347690964786</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2432085280094262</v>
+        <v>0.03835125678707108</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>39.9</v>
       </c>
       <c r="C49" t="n">
-        <v>39.41233102678765</v>
+        <v>39.71093423148177</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4876689732123509</v>
+        <v>-0.1890657685182262</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2378210274339886</v>
+        <v>0.0357458648253875</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>40.1</v>
       </c>
       <c r="C50" t="n">
-        <v>39.24870500583931</v>
+        <v>40.30340398662099</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.8512949941606962</v>
+        <v>0.2034039866209838</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7247031670830598</v>
+        <v>0.04137318177330936</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>40.6</v>
       </c>
       <c r="C51" t="n">
-        <v>39.33456577636483</v>
+        <v>40.58522491614487</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.265434223635175</v>
+        <v>-0.01477508385512749</v>
       </c>
       <c r="E51" t="n">
-        <v>1.601323774347159</v>
+        <v>0.000218303102926049</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-0.008685308628653132</v>
+        <v>0.2241264109621923</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>18.1450358373095</v>
+        <v>7.624873534645253</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.36290071674619</v>
+        <v>0.1524974706929051</v>
       </c>
     </row>
   </sheetData>

--- a/partial/sliding_window_results_window_1.xlsx
+++ b/partial/sliding_window_results_window_1.xlsx
@@ -463,13 +463,13 @@
         <v>28.98</v>
       </c>
       <c r="C2" t="n">
-        <v>29.89632680511049</v>
+        <v>28.94541488841631</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9163268051104865</v>
+        <v>-0.03458511158369504</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8396548137639914</v>
+        <v>0.001196129943256637</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.15</v>
       </c>
       <c r="C3" t="n">
-        <v>29.74049686643244</v>
+        <v>28.7991056745084</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5904968664324421</v>
+        <v>-0.3508943254915984</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3486865492665334</v>
+        <v>0.1231268276622038</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.35</v>
       </c>
       <c r="C4" t="n">
-        <v>30.17802841988026</v>
+        <v>29.33179435686392</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8280284198802619</v>
+        <v>-0.01820564313608131</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6856310641294032</v>
+        <v>0.0003314454419983444</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.37</v>
       </c>
       <c r="C5" t="n">
-        <v>29.89923241292755</v>
+        <v>29.19242328031938</v>
       </c>
       <c r="D5" t="n">
-        <v>0.529232412927545</v>
+        <v>-0.1775767196806193</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2800869468931115</v>
+        <v>0.03153349137252924</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.54</v>
       </c>
       <c r="C6" t="n">
-        <v>28.9817084540674</v>
+        <v>28.81135384383135</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5582915459325974</v>
+        <v>-0.7286461561686508</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3116894502598095</v>
+        <v>0.5309252208993499</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.55</v>
       </c>
       <c r="C7" t="n">
-        <v>29.32096095580385</v>
+        <v>29.57747694349466</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2290390441961527</v>
+        <v>0.02747694349465846</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05245888376628721</v>
+        <v>0.0007549824238086537</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.75</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6377051150338</v>
+        <v>29.50925118768227</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1122948849662038</v>
+        <v>-0.2407488123177259</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01261014118957294</v>
+        <v>0.05795999063239562</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>29.84</v>
       </c>
       <c r="C9" t="n">
-        <v>30.13562491976559</v>
+        <v>30.12048310883472</v>
       </c>
       <c r="D9" t="n">
-        <v>0.29562491976559</v>
+        <v>0.2804831088347157</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08739409318641153</v>
+        <v>0.07867077434158698</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>29.81</v>
       </c>
       <c r="C10" t="n">
-        <v>30.02736367531402</v>
+        <v>29.98628804312925</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2173636753140187</v>
+        <v>0.1762880431292508</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04724696734601813</v>
+        <v>0.0310774741503406</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>29.92</v>
       </c>
       <c r="C11" t="n">
-        <v>29.79807864747706</v>
+        <v>29.93189107453608</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1219213525229428</v>
+        <v>0.01189107453607718</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01486481620102369</v>
+        <v>0.0001413976536225432</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>29.98</v>
       </c>
       <c r="C12" t="n">
-        <v>29.73481586349194</v>
+        <v>29.61717415317793</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2451841365080618</v>
+        <v>-0.3628258468220729</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06011526079520389</v>
+        <v>0.1316425951221543</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.04</v>
       </c>
       <c r="C13" t="n">
-        <v>29.74052743269053</v>
+        <v>29.87248413530651</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2994725673094685</v>
+        <v>-0.1675158646934918</v>
       </c>
       <c r="E13" t="n">
-        <v>0.08968381857092413</v>
+        <v>0.02806156492400825</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.21</v>
       </c>
       <c r="C14" t="n">
-        <v>29.81772104667583</v>
+        <v>29.75215113902015</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3922789533241691</v>
+        <v>-0.4578488609798548</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1538827772211056</v>
+        <v>0.2096255795005504</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.22</v>
       </c>
       <c r="C15" t="n">
-        <v>29.83126696289785</v>
+        <v>30.01068969690472</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3887330371021527</v>
+        <v>-0.2093103030952754</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1511133741346636</v>
+        <v>0.04381080298183607</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.38</v>
       </c>
       <c r="C16" t="n">
-        <v>29.97346329811299</v>
+        <v>30.06591482334048</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4065367018870063</v>
+        <v>-0.3140851766595176</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1652720899811646</v>
+        <v>0.09864949819724039</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.44</v>
       </c>
       <c r="C17" t="n">
-        <v>30.04707284956853</v>
+        <v>30.54139858536893</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.392927150431472</v>
+        <v>0.1013985853689263</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1543917455461966</v>
+        <v>0.01028167311481944</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.48</v>
       </c>
       <c r="C18" t="n">
-        <v>29.91660694866449</v>
+        <v>30.36212290623091</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5633930513355061</v>
+        <v>-0.1178770937690921</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3174117302931322</v>
+        <v>0.01389500923544732</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>30.69</v>
       </c>
       <c r="C19" t="n">
-        <v>29.99936347057776</v>
+        <v>30.43712907003576</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6906365294222425</v>
+        <v>-0.2528709299642458</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4769788157724</v>
+        <v>0.06394370722098248</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>30.75</v>
       </c>
       <c r="C20" t="n">
-        <v>30.42549840475123</v>
+        <v>30.49699861175704</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3245015952487691</v>
+        <v>-0.2530013882429643</v>
       </c>
       <c r="E20" t="n">
-        <v>0.105301285318996</v>
+        <v>0.06400970245286713</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>30.94</v>
       </c>
       <c r="C21" t="n">
-        <v>30.47888267616282</v>
+        <v>30.58464022941965</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4611173238371791</v>
+        <v>-0.3553597705803497</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2126291863427619</v>
+        <v>0.1262805665469188</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>30.95</v>
       </c>
       <c r="C22" t="n">
-        <v>30.71352857353821</v>
+        <v>30.71328920570019</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2364714264617938</v>
+        <v>-0.2367107942998139</v>
       </c>
       <c r="E22" t="n">
-        <v>0.05591873553287553</v>
+        <v>0.05603200013804881</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.02</v>
       </c>
       <c r="C23" t="n">
-        <v>30.96141697364089</v>
+        <v>31.10155518028708</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05858302635910917</v>
+        <v>0.08155518028707931</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00343197097739208</v>
+        <v>0.00665124743165801</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.12</v>
       </c>
       <c r="C24" t="n">
-        <v>31.1678367404652</v>
+        <v>31.35518013655217</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04783674046520048</v>
+        <v>0.2351801365521702</v>
       </c>
       <c r="E24" t="n">
-        <v>0.002288353738334949</v>
+        <v>0.05530969662869741</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.28</v>
       </c>
       <c r="C25" t="n">
-        <v>31.10946212854389</v>
+        <v>31.38487127621416</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1705378714561085</v>
+        <v>0.1048712762141548</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0290831656007802</v>
+        <v>0.01099798457478555</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>31.38</v>
       </c>
       <c r="C26" t="n">
-        <v>31.22930082036947</v>
+        <v>31.3856245462382</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1506991796305321</v>
+        <v>0.005624546238205852</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02271024274131539</v>
+        <v>3.16355203857156e-05</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>31.58</v>
       </c>
       <c r="C27" t="n">
-        <v>31.5887951343716</v>
+        <v>31.70020497362682</v>
       </c>
       <c r="D27" t="n">
-        <v>0.008795134371599289</v>
+        <v>0.1202049736268265</v>
       </c>
       <c r="E27" t="n">
-        <v>7.735438861448722e-05</v>
+        <v>0.01444923568462605</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>31.65</v>
       </c>
       <c r="C28" t="n">
-        <v>31.96396303559739</v>
+        <v>31.53937677261185</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3139630355973893</v>
+        <v>-0.110623227388146</v>
       </c>
       <c r="E28" t="n">
-        <v>0.09857278772152751</v>
+        <v>0.01223749843776946</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>31.88</v>
       </c>
       <c r="C29" t="n">
-        <v>32.81493599015737</v>
+        <v>32.11199356791866</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9349359901573742</v>
+        <v>0.2319935679186607</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8741053056915496</v>
+        <v>0.05382101555563022</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>32.28</v>
       </c>
       <c r="C30" t="n">
-        <v>32.97279510279719</v>
+        <v>32.09364154476306</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6927951027971844</v>
+        <v>-0.1863584552369417</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4799650544597612</v>
+        <v>0.03472947383829921</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>32.45</v>
       </c>
       <c r="C31" t="n">
-        <v>33.04564124508133</v>
+        <v>32.3316306648455</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5956412450813247</v>
+        <v>-0.1183693351545045</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3547884928420307</v>
+        <v>0.01401129950491942</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>32.85</v>
       </c>
       <c r="C32" t="n">
-        <v>33.20541006560473</v>
+        <v>32.94723081609967</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3554100656047297</v>
+        <v>0.09723081609966755</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1263163147331582</v>
+        <v>0.00945383159940737</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>32.9</v>
       </c>
       <c r="C33" t="n">
-        <v>33.28618459035178</v>
+        <v>33.08463145510205</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3861845903517818</v>
+        <v>0.1846314551020498</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1491385378251735</v>
+        <v>0.03408877421310023</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>33.1</v>
       </c>
       <c r="C34" t="n">
-        <v>33.33682847309746</v>
+        <v>32.86723417979729</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2368284730974537</v>
+        <v>-0.2327658202027081</v>
       </c>
       <c r="E34" t="n">
-        <v>0.05608772566967135</v>
+        <v>0.05417992705463943</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>33.4</v>
       </c>
       <c r="C35" t="n">
-        <v>33.6759927999388</v>
+        <v>33.72367127167666</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2759927999387983</v>
+        <v>0.323671271676659</v>
       </c>
       <c r="E35" t="n">
-        <v>0.07617202561805755</v>
+        <v>0.1047630921087856</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>33.7</v>
       </c>
       <c r="C36" t="n">
-        <v>33.7170788925518</v>
+        <v>33.44215108138053</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01707889255179396</v>
+        <v>-0.257848918619473</v>
       </c>
       <c r="E36" t="n">
-        <v>0.000291688570795723</v>
+        <v>0.06648606483323162</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>34.1</v>
       </c>
       <c r="C37" t="n">
-        <v>33.82441943356593</v>
+        <v>33.6607796935109</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2755805664340727</v>
+        <v>-0.4392203064890978</v>
       </c>
       <c r="E37" t="n">
-        <v>0.07594464859612435</v>
+        <v>0.192914477632377</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>34.4</v>
       </c>
       <c r="C38" t="n">
-        <v>34.25753728015376</v>
+        <v>34.04463711618542</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.142462719846236</v>
+        <v>-0.3553628838145784</v>
       </c>
       <c r="E38" t="n">
-        <v>0.02029562654598714</v>
+        <v>0.1262827791930135</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>34.9</v>
       </c>
       <c r="C39" t="n">
-        <v>34.55309186796224</v>
+        <v>34.67609587047713</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3469081320377612</v>
+        <v>-0.2239041295228645</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1203452520739287</v>
+        <v>0.0501330592173917</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>35.3</v>
       </c>
       <c r="C40" t="n">
-        <v>35.46894970214569</v>
+        <v>35.4942175113589</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1689497021456958</v>
+        <v>0.1942175113589002</v>
       </c>
       <c r="E40" t="n">
-        <v>0.02854400185511934</v>
+        <v>0.03772044171844453</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>35.7</v>
       </c>
       <c r="C41" t="n">
-        <v>35.73876694052214</v>
+        <v>35.76531902874327</v>
       </c>
       <c r="D41" t="n">
-        <v>0.03876694052213736</v>
+        <v>0.06531902874326789</v>
       </c>
       <c r="E41" t="n">
-        <v>0.001502875677446936</v>
+        <v>0.004266575515963857</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>36.3</v>
       </c>
       <c r="C42" t="n">
-        <v>36.10449998253414</v>
+        <v>36.21823738403342</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1955000174658537</v>
+        <v>-0.08176261596657497</v>
       </c>
       <c r="E42" t="n">
-        <v>0.03822025682914908</v>
+        <v>0.00668512536969762</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>36.8</v>
       </c>
       <c r="C43" t="n">
-        <v>36.68021591248571</v>
+        <v>36.75797308388083</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.119784087514283</v>
+        <v>-0.04202691611916975</v>
       </c>
       <c r="E43" t="n">
-        <v>0.01434822762162942</v>
+        <v>0.00176626167848773</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>37.3</v>
       </c>
       <c r="C44" t="n">
-        <v>36.80267619744119</v>
+        <v>36.89594022659953</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4973238025588103</v>
+        <v>-0.4040597734004692</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2473309645915545</v>
+        <v>0.1632643004804385</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>37.9</v>
       </c>
       <c r="C45" t="n">
-        <v>37.74713299675034</v>
+        <v>37.46895399678464</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1528670032496606</v>
+        <v>-0.4310460032153571</v>
       </c>
       <c r="E45" t="n">
-        <v>0.02336832068253175</v>
+        <v>0.1858006568879337</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>38.5</v>
       </c>
       <c r="C46" t="n">
-        <v>38.41971972881053</v>
+        <v>38.31134362311996</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.08028027118946568</v>
+        <v>-0.18865637688004</v>
       </c>
       <c r="E46" t="n">
-        <v>0.006444921942254153</v>
+        <v>0.03559122853750369</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>38.9</v>
       </c>
       <c r="C47" t="n">
-        <v>39.09180267373289</v>
+        <v>38.86396156656706</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1918026737328873</v>
+        <v>-0.03603843343293534</v>
       </c>
       <c r="E47" t="n">
-        <v>0.03678826565108441</v>
+        <v>0.001298768684300111</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>39.4</v>
       </c>
       <c r="C48" t="n">
-        <v>39.59583476909648</v>
+        <v>39.31125669763671</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1958347690964786</v>
+        <v>-0.08874330236328376</v>
       </c>
       <c r="E48" t="n">
-        <v>0.03835125678707108</v>
+        <v>0.007875373714341206</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>39.9</v>
       </c>
       <c r="C49" t="n">
-        <v>39.71093423148177</v>
+        <v>39.87251888440524</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.1890657685182262</v>
+        <v>-0.0274811155947603</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0357458648253875</v>
+        <v>0.0007552117143325776</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>40.1</v>
       </c>
       <c r="C50" t="n">
-        <v>40.30340398662099</v>
+        <v>39.8999769775633</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2034039866209838</v>
+        <v>-0.200023022436703</v>
       </c>
       <c r="E50" t="n">
-        <v>0.04137318177330936</v>
+        <v>0.0400092095047138</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>40.6</v>
       </c>
       <c r="C51" t="n">
-        <v>40.58522491614487</v>
+        <v>40.10126702780719</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.01477508385512749</v>
+        <v>-0.498732972192812</v>
       </c>
       <c r="E51" t="n">
-        <v>0.000218303102926049</v>
+        <v>0.2487345775522762</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.2241264109621923</v>
+        <v>-5.959048886334198</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>7.624873534645253</v>
+        <v>3.276259258343117</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.1524974706929051</v>
+        <v>0.06552518516686233</v>
       </c>
     </row>
   </sheetData>
